--- a/ozo.xlsx
+++ b/ozo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dastanbaitursynov/Documents/GLOBERCE/oz-fmh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB904465-D106-D142-95C0-F8AC2F8957B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607BF644-9A28-F64A-8970-8E2E9D6BD324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="1020" windowWidth="27580" windowHeight="13980" xr2:uid="{3F67CEAB-F335-4518-8FB9-94B57CB73016}"/>
+    <workbookView xWindow="18540" yWindow="820" windowWidth="16120" windowHeight="19360" xr2:uid="{3F67CEAB-F335-4518-8FB9-94B57CB73016}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -193,7 +193,607 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="70">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -633,608 +1233,1448 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
-        <v>2451548</v>
+        <v>1506185</v>
       </c>
       <c r="B2" s="13">
-        <v>850000</v>
+        <v>112339</v>
       </c>
       <c r="C2" s="12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D2" s="12">
         <v>0</v>
       </c>
       <c r="E2" s="12">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="4"/>
+      <c r="A3" s="3">
+        <v>1512667</v>
+      </c>
+      <c r="B3" s="2">
+        <v>440000</v>
+      </c>
+      <c r="C3" s="4">
+        <v>11</v>
+      </c>
+      <c r="D3" s="11">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="4"/>
+      <c r="A4" s="3">
+        <v>1511969</v>
+      </c>
+      <c r="B4" s="2">
+        <v>499995</v>
+      </c>
+      <c r="C4" s="4">
+        <v>11</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="4"/>
+      <c r="A5" s="3">
+        <v>1512775</v>
+      </c>
+      <c r="B5" s="2">
+        <v>639000</v>
+      </c>
+      <c r="C5" s="4">
+        <v>11</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="4"/>
+      <c r="A6" s="3">
+        <v>1516113</v>
+      </c>
+      <c r="B6" s="2">
+        <v>172986</v>
+      </c>
+      <c r="C6" s="4">
+        <v>11</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="4"/>
+      <c r="A7" s="3">
+        <v>1516106</v>
+      </c>
+      <c r="B7" s="2">
+        <v>529990</v>
+      </c>
+      <c r="C7" s="4">
+        <v>11</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="4"/>
+      <c r="A8" s="3">
+        <v>1517973</v>
+      </c>
+      <c r="B8" s="2">
+        <v>35565</v>
+      </c>
+      <c r="C8" s="4">
+        <v>11</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="4"/>
+      <c r="A9" s="3">
+        <v>1519008</v>
+      </c>
+      <c r="B9" s="2">
+        <v>142800</v>
+      </c>
+      <c r="C9" s="4">
+        <v>11</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="4"/>
+      <c r="A10" s="3">
+        <v>1521341</v>
+      </c>
+      <c r="B10" s="2">
+        <v>171189</v>
+      </c>
+      <c r="C10" s="4">
+        <v>11</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="4"/>
+      <c r="A11" s="3">
+        <v>1520340</v>
+      </c>
+      <c r="B11" s="2">
+        <v>172986</v>
+      </c>
+      <c r="C11" s="4">
+        <v>11</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="4"/>
+      <c r="A12" s="3">
+        <v>1522253</v>
+      </c>
+      <c r="B12" s="2">
+        <v>192900</v>
+      </c>
+      <c r="C12" s="4">
+        <v>11</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="4"/>
+      <c r="A13" s="3">
+        <v>1521558</v>
+      </c>
+      <c r="B13" s="2">
+        <v>329999</v>
+      </c>
+      <c r="C13" s="4">
+        <v>11</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="4"/>
+      <c r="A14" s="3">
+        <v>1522345</v>
+      </c>
+      <c r="B14" s="2">
+        <v>339061</v>
+      </c>
+      <c r="C14" s="4">
+        <v>11</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
+      <c r="A15" s="3">
+        <v>1522042</v>
+      </c>
+      <c r="B15" s="2">
+        <v>499990</v>
+      </c>
+      <c r="C15" s="4">
+        <v>11</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
+      <c r="A16" s="3">
+        <v>1520900</v>
+      </c>
+      <c r="B16" s="2">
+        <v>678000</v>
+      </c>
+      <c r="C16" s="4">
+        <v>11</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="4"/>
+      <c r="A17" s="3">
+        <v>1521957</v>
+      </c>
+      <c r="B17" s="2">
+        <v>789800</v>
+      </c>
+      <c r="C17" s="4">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="4"/>
+      <c r="A18" s="3">
+        <v>1523285</v>
+      </c>
+      <c r="B18" s="2">
+        <v>699000</v>
+      </c>
+      <c r="C18" s="4">
+        <v>11</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
+      <c r="A19" s="3">
+        <v>1526117</v>
+      </c>
+      <c r="B19" s="2">
+        <v>308960</v>
+      </c>
+      <c r="C19" s="4">
+        <v>11</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="4"/>
+      <c r="A20" s="3">
+        <v>1527342</v>
+      </c>
+      <c r="B20" s="2">
+        <v>437899</v>
+      </c>
+      <c r="C20" s="4">
+        <v>11</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
+      <c r="A21" s="3">
+        <v>1527817</v>
+      </c>
+      <c r="B21" s="2">
+        <v>824999</v>
+      </c>
+      <c r="C21" s="4">
+        <v>11</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="4"/>
+      <c r="A22" s="3">
+        <v>1531556</v>
+      </c>
+      <c r="B22" s="2">
+        <v>15990</v>
+      </c>
+      <c r="C22" s="4">
+        <v>11</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
+      <c r="A23" s="3">
+        <v>1532327</v>
+      </c>
+      <c r="B23" s="2">
+        <v>172982</v>
+      </c>
+      <c r="C23" s="4">
+        <v>11</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="4"/>
+      <c r="A24" s="3">
+        <v>1532575</v>
+      </c>
+      <c r="B24" s="2">
+        <v>204359</v>
+      </c>
+      <c r="C24" s="4">
+        <v>11</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="4"/>
+      <c r="A25" s="3">
+        <v>1534899</v>
+      </c>
+      <c r="B25" s="2">
+        <v>143000</v>
+      </c>
+      <c r="C25" s="4">
+        <v>11</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
+      <c r="A26" s="3">
+        <v>1534892</v>
+      </c>
+      <c r="B26" s="2">
+        <v>500000</v>
+      </c>
+      <c r="C26" s="4">
+        <v>11</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4">
+        <v>14</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="4"/>
+      <c r="A27" s="3">
+        <v>1533916</v>
+      </c>
+      <c r="B27" s="2">
+        <v>660000</v>
+      </c>
+      <c r="C27" s="4">
+        <v>11</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="4"/>
+      <c r="A28" s="3">
+        <v>1533295</v>
+      </c>
+      <c r="B28" s="2">
+        <v>875000</v>
+      </c>
+      <c r="C28" s="4">
+        <v>11</v>
+      </c>
+      <c r="D28" s="5">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="4"/>
+      <c r="A29" s="3">
+        <v>1536352</v>
+      </c>
+      <c r="B29" s="2">
+        <v>503880</v>
+      </c>
+      <c r="C29" s="4">
+        <v>11</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
+      <c r="A30" s="3">
+        <v>1536623</v>
+      </c>
+      <c r="B30" s="2">
+        <v>552000</v>
+      </c>
+      <c r="C30" s="4">
+        <v>11</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="3"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
+      <c r="A31" s="3">
+        <v>1535324</v>
+      </c>
+      <c r="B31" s="2">
+        <v>875000</v>
+      </c>
+      <c r="C31" s="4">
+        <v>11</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="3"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
+      <c r="A32" s="3">
+        <v>1537466</v>
+      </c>
+      <c r="B32" s="2">
+        <v>204490</v>
+      </c>
+      <c r="C32" s="4">
+        <v>11</v>
+      </c>
+      <c r="D32" s="5">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="4"/>
+      <c r="A33" s="3">
+        <v>1537308</v>
+      </c>
+      <c r="B33" s="2">
+        <v>642300</v>
+      </c>
+      <c r="C33" s="4">
+        <v>11</v>
+      </c>
+      <c r="D33" s="5">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="4"/>
+      <c r="A34" s="3">
+        <v>1550638</v>
+      </c>
+      <c r="B34" s="2">
+        <v>140481</v>
+      </c>
+      <c r="C34" s="4">
+        <v>11</v>
+      </c>
+      <c r="D34" s="5">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="4"/>
+      <c r="A35" s="3">
+        <v>1555419</v>
+      </c>
+      <c r="B35" s="2">
+        <v>460000</v>
+      </c>
+      <c r="C35" s="4">
+        <v>11</v>
+      </c>
+      <c r="D35" s="5">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="4"/>
+      <c r="A36" s="3">
+        <v>1556420</v>
+      </c>
+      <c r="B36" s="2">
+        <v>671420</v>
+      </c>
+      <c r="C36" s="4">
+        <v>11</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="3"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="4"/>
+      <c r="A37" s="3">
+        <v>1555952</v>
+      </c>
+      <c r="B37" s="2">
+        <v>1398000</v>
+      </c>
+      <c r="C37" s="4">
+        <v>11</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="3"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="4"/>
+      <c r="A38" s="3">
+        <v>1560226</v>
+      </c>
+      <c r="B38" s="2">
+        <v>321900</v>
+      </c>
+      <c r="C38" s="4">
+        <v>11</v>
+      </c>
+      <c r="D38" s="5">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="4"/>
+      <c r="A39" s="3">
+        <v>1560296</v>
+      </c>
+      <c r="B39" s="2">
+        <v>577999</v>
+      </c>
+      <c r="C39" s="4">
+        <v>11</v>
+      </c>
+      <c r="D39" s="5">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="3"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="4"/>
+      <c r="A40" s="3">
+        <v>1565529</v>
+      </c>
+      <c r="B40" s="2">
+        <v>494997</v>
+      </c>
+      <c r="C40" s="4">
+        <v>11</v>
+      </c>
+      <c r="D40" s="5">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="4"/>
+      <c r="A41" s="3">
+        <v>1565955</v>
+      </c>
+      <c r="B41" s="2">
+        <v>864990</v>
+      </c>
+      <c r="C41" s="4">
+        <v>11</v>
+      </c>
+      <c r="D41" s="5">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="4"/>
+      <c r="A42" s="3">
+        <v>1570845</v>
+      </c>
+      <c r="B42" s="2">
+        <v>145000</v>
+      </c>
+      <c r="C42" s="4">
+        <v>11</v>
+      </c>
+      <c r="D42" s="5">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="4"/>
+      <c r="A43" s="3">
+        <v>1575384</v>
+      </c>
+      <c r="B43" s="2">
+        <v>795000</v>
+      </c>
+      <c r="C43" s="4">
+        <v>11</v>
+      </c>
+      <c r="D43" s="5">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="3"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="4"/>
+      <c r="A44" s="3">
+        <v>1579759</v>
+      </c>
+      <c r="B44" s="2">
+        <v>329990</v>
+      </c>
+      <c r="C44" s="4">
+        <v>11</v>
+      </c>
+      <c r="D44" s="5">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="4"/>
+      <c r="A45" s="3">
+        <v>1579999</v>
+      </c>
+      <c r="B45" s="2">
+        <v>738400</v>
+      </c>
+      <c r="C45" s="4">
+        <v>11</v>
+      </c>
+      <c r="D45" s="5">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="4"/>
+      <c r="A46" s="3">
+        <v>1585395</v>
+      </c>
+      <c r="B46" s="2">
+        <v>226000</v>
+      </c>
+      <c r="C46" s="4">
+        <v>11</v>
+      </c>
+      <c r="D46" s="5">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="3"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="4"/>
+      <c r="A47" s="3">
+        <v>1586608</v>
+      </c>
+      <c r="B47" s="2">
+        <v>497397</v>
+      </c>
+      <c r="C47" s="4">
+        <v>11</v>
+      </c>
+      <c r="D47" s="5">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="4"/>
+      <c r="A48" s="3">
+        <v>1587358</v>
+      </c>
+      <c r="B48" s="2">
+        <v>99990</v>
+      </c>
+      <c r="C48" s="4">
+        <v>11</v>
+      </c>
+      <c r="D48" s="5">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="4"/>
+      <c r="A49" s="3">
+        <v>1587896</v>
+      </c>
+      <c r="B49" s="2">
+        <v>167034</v>
+      </c>
+      <c r="C49" s="4">
+        <v>11</v>
+      </c>
+      <c r="D49" s="5">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="4"/>
+      <c r="A50" s="3">
+        <v>1589820</v>
+      </c>
+      <c r="B50" s="2">
+        <v>389200</v>
+      </c>
+      <c r="C50" s="4">
+        <v>11</v>
+      </c>
+      <c r="D50" s="5">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="4"/>
+      <c r="A51" s="3">
+        <v>1590878</v>
+      </c>
+      <c r="B51" s="2">
+        <v>484000</v>
+      </c>
+      <c r="C51" s="4">
+        <v>11</v>
+      </c>
+      <c r="D51" s="5">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="4"/>
+      <c r="A52" s="3">
+        <v>1601509</v>
+      </c>
+      <c r="B52" s="2">
+        <v>369890</v>
+      </c>
+      <c r="C52" s="4">
+        <v>11</v>
+      </c>
+      <c r="D52" s="5">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="4"/>
+      <c r="A53" s="3">
+        <v>1603362</v>
+      </c>
+      <c r="B53" s="2">
+        <v>439900</v>
+      </c>
+      <c r="C53" s="4">
+        <v>11</v>
+      </c>
+      <c r="D53" s="5">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="4"/>
+      <c r="A54" s="3">
+        <v>1602042</v>
+      </c>
+      <c r="B54" s="2">
+        <v>489000</v>
+      </c>
+      <c r="C54" s="4">
+        <v>11</v>
+      </c>
+      <c r="D54" s="5">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="4"/>
+      <c r="A55" s="3">
+        <v>1604843</v>
+      </c>
+      <c r="B55" s="2">
+        <v>18170</v>
+      </c>
+      <c r="C55" s="4">
+        <v>11</v>
+      </c>
+      <c r="D55" s="5">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="4"/>
+      <c r="A56" s="3">
+        <v>1608889</v>
+      </c>
+      <c r="B56" s="2">
+        <v>419600</v>
+      </c>
+      <c r="C56" s="4">
+        <v>11</v>
+      </c>
+      <c r="D56" s="5">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="4"/>
+      <c r="A57" s="3">
+        <v>1611907</v>
+      </c>
+      <c r="B57" s="2">
+        <v>275000</v>
+      </c>
+      <c r="C57" s="4">
+        <v>11</v>
+      </c>
+      <c r="D57" s="5">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="4"/>
+      <c r="A58" s="3">
+        <v>1619045</v>
+      </c>
+      <c r="B58" s="2">
+        <v>225000</v>
+      </c>
+      <c r="C58" s="4">
+        <v>11</v>
+      </c>
+      <c r="D58" s="5">
+        <v>0</v>
+      </c>
+      <c r="E58" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="4"/>
+      <c r="A59" s="3">
+        <v>1620256</v>
+      </c>
+      <c r="B59" s="2">
+        <v>287000</v>
+      </c>
+      <c r="C59" s="4">
+        <v>11</v>
+      </c>
+      <c r="D59" s="5">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="4"/>
+      <c r="A60" s="3">
+        <v>1619253</v>
+      </c>
+      <c r="B60" s="2">
+        <v>418801</v>
+      </c>
+      <c r="C60" s="4">
+        <v>11</v>
+      </c>
+      <c r="D60" s="5">
+        <v>0</v>
+      </c>
+      <c r="E60" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="4"/>
+      <c r="A61" s="3">
+        <v>1639950</v>
+      </c>
+      <c r="B61" s="2">
+        <v>69777</v>
+      </c>
+      <c r="C61" s="4">
+        <v>11</v>
+      </c>
+      <c r="D61" s="5">
+        <v>0</v>
+      </c>
+      <c r="E61" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="3"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="4"/>
+      <c r="A62" s="3">
+        <v>1649483</v>
+      </c>
+      <c r="B62" s="2">
+        <v>729307</v>
+      </c>
+      <c r="C62" s="4">
+        <v>11</v>
+      </c>
+      <c r="D62" s="5">
+        <v>0</v>
+      </c>
+      <c r="E62" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="4"/>
+      <c r="A63" s="3">
+        <v>1661617</v>
+      </c>
+      <c r="B63" s="2">
+        <v>234990</v>
+      </c>
+      <c r="C63" s="4">
+        <v>11</v>
+      </c>
+      <c r="D63" s="5">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="4"/>
+      <c r="A64" s="3">
+        <v>1661397</v>
+      </c>
+      <c r="B64" s="2">
+        <v>479900</v>
+      </c>
+      <c r="C64" s="4">
+        <v>11</v>
+      </c>
+      <c r="D64" s="5">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="4"/>
+      <c r="A65" s="3">
+        <v>1661397</v>
+      </c>
+      <c r="B65" s="2">
+        <v>479900</v>
+      </c>
+      <c r="C65" s="4">
+        <v>11</v>
+      </c>
+      <c r="D65" s="5">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="4"/>
+      <c r="A66" s="3">
+        <v>1716293</v>
+      </c>
+      <c r="B66" s="2">
+        <v>269824</v>
+      </c>
+      <c r="C66" s="4">
+        <v>11</v>
+      </c>
+      <c r="D66" s="5">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="4"/>
+      <c r="A67" s="3">
+        <v>1720850</v>
+      </c>
+      <c r="B67" s="2">
+        <v>676200</v>
+      </c>
+      <c r="C67" s="4">
+        <v>11</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0</v>
+      </c>
+      <c r="E67" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="3"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="4"/>
+      <c r="A68" s="3">
+        <v>1727942</v>
+      </c>
+      <c r="B68" s="2">
+        <v>175433</v>
+      </c>
+      <c r="C68" s="4">
+        <v>11</v>
+      </c>
+      <c r="D68" s="5">
+        <v>0</v>
+      </c>
+      <c r="E68" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="3"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="4"/>
+      <c r="A69" s="3">
+        <v>1741993</v>
+      </c>
+      <c r="B69" s="2">
+        <v>750000</v>
+      </c>
+      <c r="C69" s="4">
+        <v>11</v>
+      </c>
+      <c r="D69" s="5">
+        <v>0</v>
+      </c>
+      <c r="E69" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="3"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="4"/>
+      <c r="A70" s="3">
+        <v>1861234</v>
+      </c>
+      <c r="B70" s="2">
+        <v>455999</v>
+      </c>
+      <c r="C70" s="4">
+        <v>11</v>
+      </c>
+      <c r="D70" s="5">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="3"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="4"/>
+      <c r="A71" s="3">
+        <v>1863305</v>
+      </c>
+      <c r="B71" s="2">
+        <v>118976</v>
+      </c>
+      <c r="C71" s="4">
+        <v>11</v>
+      </c>
+      <c r="D71" s="5">
+        <v>0</v>
+      </c>
+      <c r="E71" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="3"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="4"/>
+      <c r="A72" s="3">
+        <v>1910148</v>
+      </c>
+      <c r="B72" s="2">
+        <v>538323</v>
+      </c>
+      <c r="C72" s="4">
+        <v>11</v>
+      </c>
+      <c r="D72" s="5">
+        <v>0</v>
+      </c>
+      <c r="E72" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="3"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="4"/>
+      <c r="A73" s="3">
+        <v>1911503</v>
+      </c>
+      <c r="B73" s="2">
+        <v>105546</v>
+      </c>
+      <c r="C73" s="4">
+        <v>11</v>
+      </c>
+      <c r="D73" s="5">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="3"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="4"/>
+      <c r="A74" s="3">
+        <v>1911817</v>
+      </c>
+      <c r="B74" s="2">
+        <v>350770</v>
+      </c>
+      <c r="C74" s="4">
+        <v>11</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0</v>
+      </c>
+      <c r="E74" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="3"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="4"/>
+      <c r="A75" s="3">
+        <v>1937698</v>
+      </c>
+      <c r="B75" s="2">
+        <v>388878</v>
+      </c>
+      <c r="C75" s="4">
+        <v>11</v>
+      </c>
+      <c r="D75" s="5">
+        <v>0</v>
+      </c>
+      <c r="E75" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="3"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="4"/>
+      <c r="A76" s="3">
+        <v>1954989</v>
+      </c>
+      <c r="B76" s="2">
+        <v>210156</v>
+      </c>
+      <c r="C76" s="4">
+        <v>11</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0</v>
+      </c>
+      <c r="E76" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="3"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="4"/>
+      <c r="A77" s="3">
+        <v>1957398</v>
+      </c>
+      <c r="B77" s="2">
+        <v>99999</v>
+      </c>
+      <c r="C77" s="4">
+        <v>11</v>
+      </c>
+      <c r="D77" s="5">
+        <v>0</v>
+      </c>
+      <c r="E77" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="3"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="4"/>
+      <c r="A78" s="3">
+        <v>2000177</v>
+      </c>
+      <c r="B78" s="2">
+        <v>199989</v>
+      </c>
+      <c r="C78" s="4">
+        <v>11</v>
+      </c>
+      <c r="D78" s="5">
+        <v>0</v>
+      </c>
+      <c r="E78" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="3"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="4"/>
+      <c r="A79" s="3">
+        <v>2029806</v>
+      </c>
+      <c r="B79" s="2">
+        <v>222999</v>
+      </c>
+      <c r="C79" s="4">
+        <v>11</v>
+      </c>
+      <c r="D79" s="5">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="3"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="4"/>
+      <c r="A80" s="3">
+        <v>1533432</v>
+      </c>
+      <c r="B80" s="2">
+        <v>726890</v>
+      </c>
+      <c r="C80" s="4">
+        <v>18</v>
+      </c>
+      <c r="D80" s="5">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4">
+        <v>21</v>
+      </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="3"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="4"/>
+      <c r="A81" s="3">
+        <v>1599684</v>
+      </c>
+      <c r="B81" s="2">
+        <v>720000</v>
+      </c>
+      <c r="C81" s="4">
+        <v>18</v>
+      </c>
+      <c r="D81" s="5">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4">
+        <v>22</v>
+      </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="3"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="4"/>
+      <c r="A82" s="3">
+        <v>1613211</v>
+      </c>
+      <c r="B82" s="2">
+        <v>1999900</v>
+      </c>
+      <c r="C82" s="4">
+        <v>18</v>
+      </c>
+      <c r="D82" s="5">
+        <v>0</v>
+      </c>
+      <c r="E82" s="4">
+        <v>22</v>
+      </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="3"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="4"/>
+      <c r="A83" s="3">
+        <v>1913919</v>
+      </c>
+      <c r="B83" s="2">
+        <v>447990</v>
+      </c>
+      <c r="C83" s="4">
+        <v>18</v>
+      </c>
+      <c r="D83" s="5">
+        <v>0</v>
+      </c>
+      <c r="E83" s="4">
+        <v>21</v>
+      </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="3"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="4"/>
+      <c r="A84" s="3">
+        <v>1985687</v>
+      </c>
+      <c r="B84" s="2">
+        <v>2384937</v>
+      </c>
+      <c r="C84" s="4">
+        <v>18</v>
+      </c>
+      <c r="D84" s="5">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4">
+        <v>21</v>
+      </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="3"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="4"/>
+      <c r="A85" s="3">
+        <v>2023662</v>
+      </c>
+      <c r="B85" s="2">
+        <v>89400</v>
+      </c>
+      <c r="C85" s="4">
+        <v>18</v>
+      </c>
+      <c r="D85" s="5">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4">
+        <v>21</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="3"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="4"/>
+      <c r="A86" s="3">
+        <v>2041581</v>
+      </c>
+      <c r="B86" s="2">
+        <v>114741</v>
+      </c>
+      <c r="C86" s="4">
+        <v>18</v>
+      </c>
+      <c r="D86" s="5">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4">
+        <v>21</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="3"/>
@@ -1252,16 +2692,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/ozo.xlsx
+++ b/ozo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dastanbaitursynov/Documents/GLOBERCE/oz-fmh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1263A5BE-D1A4-4C4D-9839-09D9835FAB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5E3F1D-3A4F-AC48-B228-4623698FCDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18440" yWindow="820" windowWidth="16120" windowHeight="19360" xr2:uid="{3F67CEAB-F335-4518-8FB9-94B57CB73016}"/>
   </bookViews>
@@ -228,7 +228,107 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -668,217 +768,217 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
-        <v>1451295</v>
+        <v>2507635</v>
       </c>
       <c r="B2" s="12">
-        <v>749790</v>
+        <v>184240</v>
       </c>
       <c r="C2" s="11">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D2" s="14">
         <v>0</v>
       </c>
       <c r="E2" s="11">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>1450916</v>
+        <v>2511263</v>
       </c>
       <c r="B3" s="2">
-        <v>999990</v>
+        <v>28200</v>
       </c>
       <c r="C3" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D3" s="15">
         <v>0</v>
       </c>
       <c r="E3" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>1451000</v>
+        <v>2511308</v>
       </c>
       <c r="B4" s="2">
-        <v>1999990</v>
+        <v>95880</v>
       </c>
       <c r="C4" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D4" s="15">
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>1453923</v>
+        <v>2516744</v>
       </c>
       <c r="B5" s="2">
-        <v>550000</v>
+        <v>163560</v>
       </c>
       <c r="C5" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" s="15">
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>1452434</v>
+        <v>2537733</v>
       </c>
       <c r="B6" s="2">
-        <v>643990</v>
+        <v>186120</v>
       </c>
       <c r="C6" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D6" s="15">
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>1460232</v>
+        <v>2541545</v>
       </c>
       <c r="B7" s="2">
-        <v>109790</v>
+        <v>112800</v>
       </c>
       <c r="C7" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D7" s="15">
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>1461952</v>
+        <v>2541770</v>
       </c>
       <c r="B8" s="2">
-        <v>610000</v>
+        <v>319600</v>
       </c>
       <c r="C8" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="15">
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>1463831</v>
+        <v>2542428</v>
       </c>
       <c r="B9" s="2">
-        <v>505797</v>
+        <v>157356</v>
       </c>
       <c r="C9" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D9" s="15">
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>1467285</v>
+        <v>2547414</v>
       </c>
       <c r="B10" s="2">
-        <v>108651</v>
+        <v>101520</v>
       </c>
       <c r="C10" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D10" s="15">
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <v>12.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>1468323</v>
+        <v>2565716</v>
       </c>
       <c r="B11" s="2">
-        <v>638601</v>
+        <v>50384</v>
       </c>
       <c r="C11" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D11" s="15">
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>1469482</v>
+        <v>2567506</v>
       </c>
       <c r="B12" s="2">
-        <v>499996</v>
+        <v>90240</v>
       </c>
       <c r="C12" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D12" s="15">
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>1471956</v>
+        <v>2579449</v>
       </c>
       <c r="B13" s="2">
-        <v>49491</v>
+        <v>18800</v>
       </c>
       <c r="C13" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D13" s="15">
         <v>0</v>
       </c>
       <c r="E13" s="4">
-        <v>12.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>1472205</v>
+        <v>2579652</v>
       </c>
       <c r="B14" s="2">
-        <v>523990</v>
+        <v>46172.800000000003</v>
       </c>
       <c r="C14" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="15">
         <v>0</v>
@@ -889,139 +989,89 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>1473850</v>
+        <v>2580045</v>
       </c>
       <c r="B15" s="2">
-        <v>479000</v>
+        <v>61701.599999999999</v>
       </c>
       <c r="C15" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D15" s="15">
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>1477282</v>
+        <v>2583646</v>
       </c>
       <c r="B16" s="2">
-        <v>79990</v>
+        <v>159800</v>
       </c>
       <c r="C16" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D16" s="15">
         <v>0</v>
       </c>
       <c r="E16" s="4">
-        <v>12.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>1476031</v>
+        <v>2597976</v>
       </c>
       <c r="B17" s="2">
-        <v>124490</v>
+        <v>171080</v>
       </c>
       <c r="C17" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D17" s="15">
         <v>0</v>
       </c>
       <c r="E17" s="4">
-        <v>12.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
-        <v>1479617</v>
-      </c>
-      <c r="B18" s="2">
-        <v>299990</v>
-      </c>
-      <c r="C18" s="4">
-        <v>11</v>
-      </c>
-      <c r="D18" s="15">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>13</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>1478730</v>
-      </c>
-      <c r="B19" s="2">
-        <v>300000</v>
-      </c>
-      <c r="C19" s="4">
-        <v>11</v>
-      </c>
-      <c r="D19" s="15">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4">
-        <v>14</v>
-      </c>
+      <c r="A19" s="3"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
-        <v>1478704</v>
-      </c>
-      <c r="B20" s="2">
-        <v>559070</v>
-      </c>
-      <c r="C20" s="4">
-        <v>11</v>
-      </c>
-      <c r="D20" s="15">
-        <v>0</v>
-      </c>
-      <c r="E20" s="4">
-        <v>12.5</v>
-      </c>
+      <c r="A20" s="3"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
-        <v>1481478</v>
-      </c>
-      <c r="B21" s="2">
-        <v>508889</v>
-      </c>
-      <c r="C21" s="4">
-        <v>11</v>
-      </c>
-      <c r="D21" s="15">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
-        <v>13</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>1486454</v>
-      </c>
-      <c r="B22" s="2">
-        <v>357940</v>
-      </c>
-      <c r="C22" s="4">
-        <v>11</v>
-      </c>
-      <c r="D22" s="15">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>12.5</v>
-      </c>
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
@@ -1487,16 +1537,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
